--- a/planweb_policy.xlsx
+++ b/planweb_policy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a9756\Documents\nsx2aitrust\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\go_pratice\firewall-policy-sync\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0464E7-2E61-4391-B046-147A20250104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285D7BE5-0BC3-4023-94F6-2D512025DCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2690" yWindow="2650" windowWidth="16270" windowHeight="11170" xr2:uid="{02FDE031-BBF9-49CF-85AC-6844A8CDBF0E}"/>
+    <workbookView xWindow="2640" yWindow="3135" windowWidth="24420" windowHeight="12345" xr2:uid="{02FDE031-BBF9-49CF-85AC-6844A8CDBF0E}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="35">
   <si>
     <t>Rule Name</t>
   </si>
@@ -140,12 +140,21 @@
   <si>
     <t>Port / Service(s)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>api產生, 給使用者用的</t>
+  </si>
+  <si>
+    <t>trustone外連出去</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -203,7 +212,9 @@
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{4EFA2C33-3565-49EB-B4C8-2A2584A04DF8}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -532,17 +543,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F6F752-F714-4325-873B-17DA167582FD}">
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.75" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="29.54296875" customWidth="1"/>
-    <col min="4" max="4" width="11.26953125" customWidth="1"/>
+    <col min="3" max="3" width="29.5" customWidth="1"/>
+    <col min="4" max="4" width="11.25" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,8 +569,11 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -575,8 +589,11 @@
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -592,8 +609,11 @@
       <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -609,8 +629,11 @@
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -626,8 +649,11 @@
       <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -643,8 +669,11 @@
       <c r="E6" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -660,8 +689,11 @@
       <c r="E7" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -677,8 +709,11 @@
       <c r="E8" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -694,8 +729,11 @@
       <c r="E9" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -711,8 +749,11 @@
       <c r="E10" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -728,8 +769,11 @@
       <c r="E11" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -745,8 +789,11 @@
       <c r="E12" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -762,8 +809,11 @@
       <c r="E13" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -779,8 +829,11 @@
       <c r="E14" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -796,8 +849,11 @@
       <c r="E15" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -813,8 +869,11 @@
       <c r="E16" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -830,8 +889,11 @@
       <c r="E17" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -847,8 +909,11 @@
       <c r="E18" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -864,8 +929,11 @@
       <c r="E19" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -881,8 +949,11 @@
       <c r="E20" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -898,8 +969,11 @@
       <c r="E21" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -915,8 +989,11 @@
       <c r="E22" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -932,8 +1009,11 @@
       <c r="E23" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -949,8 +1029,11 @@
       <c r="E24" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -966,8 +1049,11 @@
       <c r="E25" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -983,8 +1069,11 @@
       <c r="E26" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -1000,8 +1089,11 @@
       <c r="E27" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -1017,8 +1109,11 @@
       <c r="E28" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1034,8 +1129,11 @@
       <c r="E29" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -1051,8 +1149,11 @@
       <c r="E30" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>22</v>
       </c>
@@ -1068,8 +1169,11 @@
       <c r="E31" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -1085,8 +1189,11 @@
       <c r="E32" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>22</v>
       </c>
@@ -1102,8 +1209,11 @@
       <c r="E33" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>22</v>
       </c>
@@ -1118,6 +1228,9 @@
       </c>
       <c r="E34" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="F34" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
